--- a/12607125.xlsx
+++ b/12607125.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anuka\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anuka\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5F1F67-10C7-4A63-A4FA-FC485DB7EE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5067808-913F-4429-A577-4F0170FC6308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -242,6 +242,99 @@
   </si>
   <si>
     <t>Had a busy day with classes and study, felt neutral but satisfied.</t>
+  </si>
+  <si>
+    <t>Attended classes and studied, but felt neutral with low energy.</t>
+  </si>
+  <si>
+    <t>Had a productive day with classes and study, felt good and satisfied.</t>
+  </si>
+  <si>
+    <t>Had a regular day with classes and study, felt neutral overall.</t>
+  </si>
+  <si>
+    <t>Focused on study and other activities, felt good and satisfied.</t>
+  </si>
+  <si>
+    <t>Had a productive day with good study time and activities, felt good overall.</t>
+  </si>
+  <si>
+    <t>Attended classes and studied, felt neutral but satisfied.</t>
+  </si>
+  <si>
+    <t>Had a busy day with classes and study, felt neutral overall.</t>
+  </si>
+  <si>
+    <t>Had a tiring day with lower energy and felt unsatisfied.</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Attended classes and worked on coding and other activities, felt neutral overall.</t>
+  </si>
+  <si>
+    <t>Attended classes and spent time studying and on other activities, felt good overall.</t>
+  </si>
+  <si>
+    <t>Spent the day at a friend’s house and enjoyed some time together.</t>
+  </si>
+  <si>
+    <t>Continued spending time at my friend’s house and had a relaxing day.</t>
+  </si>
+  <si>
+    <t>Returned home and settled back into my routine.</t>
+  </si>
+  <si>
+    <t>2026-09-</t>
+  </si>
+  <si>
+    <t>Attended classes and studied, had a normal day and felt neutral overall.</t>
+  </si>
+  <si>
+    <t>Attended classes and stayed productive, felt good but neutral about the day.</t>
+  </si>
+  <si>
+    <t>Attended classes and studied well, felt good and satisfied.</t>
+  </si>
+  <si>
+    <t>Had a productive day with study and other activities, felt good and satisfied.</t>
+  </si>
+  <si>
+    <t>Spent time studying and on other activities, felt good overall.</t>
+  </si>
+  <si>
+    <t>Attended classes and stayed productive, felt good and satisfied.</t>
+  </si>
+  <si>
+    <t>Attended classes and studied, but felt neutral overall.</t>
+  </si>
+  <si>
+    <t>Attended the fresher party at the university and had a great time.</t>
+  </si>
+  <si>
+    <t>Visited a friend’s house and spent the day relaxing.</t>
+  </si>
+  <si>
+    <t>Continued spending time at a friend’s house and enjoyed the day.</t>
+  </si>
+  <si>
+    <t>Spent the day at a friend’s house before returning to my routine.</t>
+  </si>
+  <si>
+    <t>Had a tiring day with low energy and felt unsatisfied.</t>
+  </si>
+  <si>
+    <t>Had a regular day with some study and activities, but felt unsatisfied.</t>
+  </si>
+  <si>
+    <t>Attended classes and studied, felt good and satisfied.</t>
+  </si>
+  <si>
+    <t>Had a relaxed day with some study and activities, felt good and satisfied.</t>
+  </si>
+  <si>
+    <t>Spent a quiet day with some study and activities, but felt neutral and unsatisfied.</t>
   </si>
 </sst>
 </file>
@@ -1406,7 +1499,7 @@
         <v>33</v>
       </c>
       <c r="F14" s="14">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="G14" s="14">
         <v>7</v>
@@ -1416,11 +1509,11 @@
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>1064</v>
+        <v>994</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>376</v>
+        <v>446</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>58</v>
@@ -1435,736 +1528,1528 @@
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
         <v>46253</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="B15" s="14">
+        <v>402</v>
+      </c>
+      <c r="C15" s="14">
+        <v>25</v>
+      </c>
+      <c r="D15" s="14">
+        <v>87</v>
+      </c>
+      <c r="E15" s="14">
+        <v>23</v>
+      </c>
+      <c r="F15" s="14">
+        <v>350</v>
+      </c>
+      <c r="G15" s="14">
+        <v>7</v>
+      </c>
+      <c r="H15" s="14">
+        <v>73</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+        <v>480</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B16" s="14">
+        <v>386</v>
+      </c>
+      <c r="C16" s="14">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
+        <v>121</v>
+      </c>
+      <c r="E16" s="14">
+        <v>35</v>
+      </c>
+      <c r="F16" s="14">
+        <v>200</v>
+      </c>
+      <c r="G16" s="14">
+        <v>4</v>
+      </c>
+      <c r="H16" s="14">
+        <v>108</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+        <v>570</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B17" s="14">
+        <v>402</v>
+      </c>
+      <c r="C17" s="14">
+        <v>22</v>
+      </c>
+      <c r="D17" s="14">
+        <v>108</v>
+      </c>
+      <c r="E17" s="14">
+        <v>32</v>
+      </c>
+      <c r="F17" s="14">
+        <v>250</v>
+      </c>
+      <c r="G17" s="14">
+        <v>5</v>
+      </c>
+      <c r="H17" s="14">
+        <v>97</v>
+      </c>
+      <c r="I17" s="15">
+        <f>IF(SUM(B17:F17,H17)=0,"",SUM(B17:F17,H17))</f>
+        <v>911</v>
+      </c>
+      <c r="J17" s="15">
+        <f t="shared" si="1"/>
+        <v>529</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B18" s="14">
+        <v>468</v>
+      </c>
+      <c r="C18" s="14">
+        <v>25</v>
+      </c>
+      <c r="D18" s="14">
+        <v>132</v>
+      </c>
+      <c r="E18" s="14">
+        <v>42</v>
+      </c>
+      <c r="F18" s="14">
+        <v>0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>0</v>
+      </c>
+      <c r="H18" s="14">
+        <v>185</v>
+      </c>
+      <c r="I18" s="15">
+        <f t="shared" ref="I18" si="2">IF(SUM(B18:F18,H18)=0,"",SUM(B18:F18,H18))</f>
+        <v>852</v>
+      </c>
+      <c r="J18" s="15">
+        <f t="shared" ref="J18" si="3">IF(I18="","",1440-I18)</f>
+        <v>588</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B19" s="14">
+        <v>502</v>
+      </c>
+      <c r="C19" s="14">
+        <v>27</v>
+      </c>
+      <c r="D19" s="14">
+        <v>138</v>
+      </c>
+      <c r="E19" s="14">
+        <v>47</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>167</v>
+      </c>
+      <c r="I19" s="15">
+        <f t="shared" ref="I19" si="4">IF(SUM(B19:F19,H19)=0,"",SUM(B19:F19,H19))</f>
+        <v>881</v>
+      </c>
+      <c r="J19" s="15">
+        <f t="shared" ref="J19" si="5">IF(I19="","",1440-I19)</f>
+        <v>559</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B20" s="14">
+        <v>385</v>
+      </c>
+      <c r="C20" s="14">
+        <v>26</v>
+      </c>
+      <c r="D20" s="14">
+        <v>101</v>
+      </c>
+      <c r="E20" s="14">
+        <v>27</v>
+      </c>
+      <c r="F20" s="14">
+        <v>250</v>
+      </c>
+      <c r="G20" s="14">
+        <v>5</v>
+      </c>
+      <c r="H20" s="14">
+        <v>102</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>891</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+        <v>549</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B21" s="14">
+        <v>384</v>
+      </c>
+      <c r="C21" s="14">
+        <v>22</v>
+      </c>
+      <c r="D21" s="14">
+        <v>88</v>
+      </c>
+      <c r="E21" s="14">
+        <v>20</v>
+      </c>
+      <c r="F21" s="14">
+        <v>350</v>
+      </c>
+      <c r="G21" s="14">
+        <v>7</v>
+      </c>
+      <c r="H21" s="14">
+        <v>85</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>949</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+        <v>491</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B22" s="14">
+        <v>388</v>
+      </c>
+      <c r="C22" s="14">
+        <v>21</v>
+      </c>
+      <c r="D22" s="14">
+        <v>92</v>
+      </c>
+      <c r="E22" s="14">
+        <v>23</v>
+      </c>
+      <c r="F22" s="14">
+        <v>300</v>
+      </c>
+      <c r="G22" s="14">
+        <v>6</v>
+      </c>
+      <c r="H22" s="14">
+        <v>94</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>918</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+        <v>522</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B23" s="14">
+        <v>397</v>
+      </c>
+      <c r="C23" s="14">
+        <v>27</v>
+      </c>
+      <c r="D23" s="14">
+        <v>76</v>
+      </c>
+      <c r="E23" s="14">
+        <v>39</v>
+      </c>
+      <c r="F23" s="14">
+        <v>300</v>
+      </c>
+      <c r="G23" s="14">
+        <v>6</v>
+      </c>
+      <c r="H23" s="14">
+        <v>87</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>926</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+        <v>514</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B24" s="14">
+        <v>403</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>57</v>
+      </c>
+      <c r="E24" s="14">
+        <v>0</v>
+      </c>
+      <c r="F24" s="14">
+        <v>250</v>
+      </c>
+      <c r="G24" s="14">
+        <v>5</v>
+      </c>
+      <c r="H24" s="14">
+        <v>256</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>966</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+        <v>474</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B25" s="14">
+        <v>443</v>
+      </c>
+      <c r="C25" s="14">
+        <v>21</v>
+      </c>
+      <c r="D25" s="14">
+        <v>0</v>
+      </c>
+      <c r="E25" s="14">
+        <v>0</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>389</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>853</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+        <v>587</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B26" s="14">
+        <v>434</v>
+      </c>
+      <c r="C26" s="14">
+        <v>0</v>
+      </c>
+      <c r="D26" s="14">
+        <v>0</v>
+      </c>
+      <c r="E26" s="14">
+        <v>0</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>456</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+        <v>550</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B27" s="14">
+        <v>408</v>
+      </c>
+      <c r="C27" s="14">
+        <v>23</v>
+      </c>
+      <c r="D27" s="14">
+        <v>88</v>
+      </c>
+      <c r="E27" s="14">
+        <v>43</v>
+      </c>
+      <c r="F27" s="14">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14">
+        <v>102</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>664</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+        <v>776</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B28" s="14">
+        <v>398</v>
+      </c>
+      <c r="C28" s="14">
+        <v>27</v>
+      </c>
+      <c r="D28" s="14">
+        <v>76</v>
+      </c>
+      <c r="E28" s="14">
+        <v>34</v>
+      </c>
+      <c r="F28" s="14">
+        <v>350</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="14">
+        <v>78</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>963</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+        <v>477</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B29" s="14">
+        <v>402</v>
+      </c>
+      <c r="C29" s="14">
+        <v>28</v>
+      </c>
+      <c r="D29" s="14">
+        <v>83</v>
+      </c>
+      <c r="E29" s="14">
+        <v>28</v>
+      </c>
+      <c r="F29" s="14">
+        <v>300</v>
+      </c>
+      <c r="G29" s="14">
+        <v>6</v>
+      </c>
+      <c r="H29" s="14">
+        <v>108</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>949</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+        <v>491</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B30" s="14">
+        <v>403</v>
+      </c>
+      <c r="C30" s="14">
+        <v>28</v>
+      </c>
+      <c r="D30" s="14">
+        <v>84</v>
+      </c>
+      <c r="E30" s="14">
+        <v>29</v>
+      </c>
+      <c r="F30" s="14">
+        <v>200</v>
+      </c>
+      <c r="G30" s="14">
+        <v>4</v>
+      </c>
+      <c r="H30" s="14">
+        <v>112</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>856</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+        <v>584</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B31" s="14">
+        <v>401</v>
+      </c>
+      <c r="C31" s="14">
+        <v>27</v>
+      </c>
+      <c r="D31" s="14">
+        <v>87</v>
+      </c>
+      <c r="E31" s="14">
+        <v>28</v>
+      </c>
+      <c r="F31" s="14">
+        <v>200</v>
+      </c>
+      <c r="G31" s="14">
+        <v>4</v>
+      </c>
+      <c r="H31" s="14">
+        <v>167</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+        <v>530</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B32" s="14">
+        <v>422</v>
+      </c>
+      <c r="C32" s="14">
+        <v>22</v>
+      </c>
+      <c r="D32" s="14">
+        <v>43</v>
+      </c>
+      <c r="E32" s="14">
+        <v>15</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>189</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>691</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+        <v>749</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B33" s="14">
+        <v>432</v>
+      </c>
+      <c r="C33" s="14">
+        <v>27</v>
+      </c>
+      <c r="D33" s="14">
+        <v>68</v>
+      </c>
+      <c r="E33" s="14">
+        <v>22</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>112</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>661</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+        <v>779</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B34" s="14">
+        <v>389</v>
+      </c>
+      <c r="C34" s="14">
+        <v>27</v>
+      </c>
+      <c r="D34" s="14">
+        <v>81</v>
+      </c>
+      <c r="E34" s="14">
+        <v>18</v>
+      </c>
+      <c r="F34" s="14">
+        <v>250</v>
+      </c>
+      <c r="G34" s="14">
+        <v>5</v>
+      </c>
+      <c r="H34" s="14">
+        <v>108</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>873</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+        <v>567</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B35" s="14">
+        <v>381</v>
+      </c>
+      <c r="C35" s="14">
+        <v>22</v>
+      </c>
+      <c r="D35" s="14">
+        <v>78</v>
+      </c>
+      <c r="E35" s="14">
+        <v>21</v>
+      </c>
+      <c r="F35" s="14">
+        <v>350</v>
+      </c>
+      <c r="G35" s="14">
+        <v>7</v>
+      </c>
+      <c r="H35" s="14">
+        <v>87</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>939</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+        <v>501</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B36" s="14">
+        <v>388</v>
+      </c>
+      <c r="C36" s="14">
+        <v>23</v>
+      </c>
+      <c r="D36" s="14">
+        <v>67</v>
+      </c>
+      <c r="E36" s="14">
+        <v>23</v>
+      </c>
+      <c r="F36" s="14">
+        <v>300</v>
+      </c>
+      <c r="G36" s="14">
+        <v>6</v>
+      </c>
+      <c r="H36" s="14">
+        <v>101</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>902</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+        <v>538</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B37" s="14">
+        <v>381</v>
+      </c>
+      <c r="C37" s="14">
+        <v>32</v>
+      </c>
+      <c r="D37" s="14">
+        <v>0</v>
+      </c>
+      <c r="E37" s="14">
+        <v>0</v>
+      </c>
+      <c r="F37" s="14">
+        <v>150</v>
+      </c>
+      <c r="G37" s="14">
+        <v>3</v>
+      </c>
+      <c r="H37" s="14">
+        <v>330</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>893</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+        <v>547</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B38" s="14">
+        <v>398</v>
+      </c>
+      <c r="C38" s="14">
+        <v>0</v>
+      </c>
+      <c r="D38" s="14">
+        <v>0</v>
+      </c>
+      <c r="E38" s="14">
+        <v>0</v>
+      </c>
+      <c r="F38" s="14">
+        <v>250</v>
+      </c>
+      <c r="G38" s="14">
+        <v>5</v>
+      </c>
+      <c r="H38" s="14">
+        <v>250</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>898</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+        <v>542</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B39" s="14">
+        <v>401</v>
+      </c>
+      <c r="C39" s="14">
+        <v>0</v>
+      </c>
+      <c r="D39" s="14">
+        <v>0</v>
+      </c>
+      <c r="E39" s="14">
+        <v>0</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>280</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>681</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+        <v>759</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B40" s="14">
+        <v>420</v>
+      </c>
+      <c r="C40" s="14">
+        <v>0</v>
+      </c>
+      <c r="D40" s="14">
+        <v>0</v>
+      </c>
+      <c r="E40" s="14">
+        <v>0</v>
+      </c>
+      <c r="F40" s="14">
+        <v>0</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>223</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>643</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+        <v>797</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B41" s="14">
+        <v>388</v>
+      </c>
+      <c r="C41" s="14">
+        <v>33</v>
+      </c>
+      <c r="D41" s="14">
+        <v>66</v>
+      </c>
+      <c r="E41" s="14">
+        <v>23</v>
+      </c>
+      <c r="F41" s="14">
+        <v>250</v>
+      </c>
+      <c r="G41" s="14">
+        <v>5</v>
+      </c>
+      <c r="H41" s="14">
+        <v>101</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>861</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+        <v>579</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B42" s="14">
+        <v>382</v>
+      </c>
+      <c r="C42" s="14">
+        <v>28</v>
+      </c>
+      <c r="D42" s="14">
+        <v>68</v>
+      </c>
+      <c r="E42" s="14">
+        <v>23</v>
+      </c>
+      <c r="F42" s="14">
+        <v>350</v>
+      </c>
+      <c r="G42" s="14">
+        <v>7</v>
+      </c>
+      <c r="H42" s="14">
+        <v>97</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>948</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+        <v>492</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B43" s="14">
+        <v>388</v>
+      </c>
+      <c r="C43" s="14">
+        <v>23</v>
+      </c>
+      <c r="D43" s="14">
+        <v>30</v>
+      </c>
+      <c r="E43" s="14">
+        <v>20</v>
+      </c>
+      <c r="F43" s="14">
+        <v>300</v>
+      </c>
+      <c r="G43" s="14">
+        <v>6</v>
+      </c>
+      <c r="H43" s="14">
+        <v>110</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>871</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+        <v>569</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B44" s="14">
+        <v>398</v>
+      </c>
+      <c r="C44" s="14">
+        <v>25</v>
+      </c>
+      <c r="D44" s="14">
+        <v>32</v>
+      </c>
+      <c r="E44" s="14">
+        <v>22</v>
+      </c>
+      <c r="F44" s="14">
+        <v>200</v>
+      </c>
+      <c r="G44" s="14">
+        <v>4</v>
+      </c>
+      <c r="H44" s="14">
+        <v>88</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>765</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+        <v>675</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B45" s="14">
+        <v>372</v>
+      </c>
+      <c r="C45" s="14">
+        <v>27</v>
+      </c>
+      <c r="D45" s="14">
+        <v>68</v>
+      </c>
+      <c r="E45" s="14">
+        <v>0</v>
+      </c>
+      <c r="F45" s="14">
+        <v>250</v>
+      </c>
+      <c r="G45" s="14">
+        <v>5</v>
+      </c>
+      <c r="H45" s="14">
+        <v>74</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>791</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+        <v>649</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B46" s="14">
+        <v>402</v>
+      </c>
+      <c r="C46" s="14">
+        <v>22</v>
+      </c>
+      <c r="D46" s="14">
+        <v>45</v>
+      </c>
+      <c r="E46" s="14">
+        <v>0</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
+      <c r="G46" s="14">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>167</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>636</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+        <v>804</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B47" s="14">
+        <v>410</v>
+      </c>
+      <c r="C47" s="14">
+        <v>0</v>
+      </c>
+      <c r="D47" s="14">
+        <v>44</v>
+      </c>
+      <c r="E47" s="14">
+        <v>0</v>
+      </c>
+      <c r="F47" s="14">
+        <v>0</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>187</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>641</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="13"/>
+        <v>799</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="13">
+        <v>46286</v>
+      </c>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
       <c r="D48" s="14"/>
@@ -2186,7 +3071,9 @@
       <c r="N48" s="17"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="13"/>
+      <c r="A49" s="13" t="s">
+        <v>83</v>
+      </c>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
       <c r="D49" s="14"/>
@@ -2208,7 +3095,9 @@
       <c r="N49" s="17"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="13"/>
+      <c r="A50" s="13" t="s">
+        <v>83</v>
+      </c>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
@@ -2230,7 +3119,9 @@
       <c r="N50" s="17"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="13"/>
+      <c r="A51" s="13" t="s">
+        <v>83</v>
+      </c>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
       <c r="D51" s="14"/>
@@ -2252,7 +3143,9 @@
       <c r="N51" s="17"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A52" s="13"/>
+      <c r="A52" s="13" t="s">
+        <v>83</v>
+      </c>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
       <c r="D52" s="14"/>
@@ -2274,7 +3167,9 @@
       <c r="N52" s="17"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A53" s="13"/>
+      <c r="A53" s="13" t="s">
+        <v>83</v>
+      </c>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
       <c r="D53" s="14"/>
@@ -2657,11 +3552,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="6">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="7">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2679,11 +3574,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2701,11 +3596,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2723,11 +3618,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -2745,11 +3640,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -2767,11 +3662,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -2789,11 +3684,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -2811,11 +3706,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -2833,11 +3728,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -2855,11 +3750,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -2877,11 +3772,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -2899,11 +3794,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -2921,11 +3816,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -2943,11 +3838,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -2965,11 +3860,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -2987,11 +3882,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3009,11 +3904,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3031,11 +3926,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3053,11 +3948,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3075,11 +3970,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3097,11 +3992,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3119,11 +4014,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3141,11 +4036,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3163,11 +4058,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3185,11 +4080,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3207,11 +4102,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3229,11 +4124,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3251,11 +4146,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3273,11 +4168,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3295,11 +4190,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3317,11 +4212,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3339,11 +4234,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3361,11 +4256,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3383,11 +4278,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3405,11 +4300,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3427,11 +4322,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3449,11 +4344,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3471,11 +4366,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3493,11 +4388,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3515,11 +4410,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3537,11 +4432,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3559,11 +4454,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3581,11 +4476,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3603,11 +4498,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3625,11 +4520,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3647,11 +4542,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3669,11 +4564,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3691,11 +4586,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -3713,11 +4608,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -3735,11 +4630,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -3757,11 +4652,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -3779,11 +4674,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -3801,11 +4696,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -3823,11 +4718,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -3845,11 +4740,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -3867,11 +4762,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -3889,11 +4784,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -3911,11 +4806,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -3933,11 +4828,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -3955,11 +4850,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -3977,11 +4872,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -3999,11 +4894,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4021,11 +4916,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4043,11 +4938,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4065,11 +4960,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="8">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="9">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4087,11 +4982,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4109,11 +5004,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4131,11 +5026,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4153,11 +5048,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4175,11 +5070,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4197,11 +5092,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4219,11 +5114,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4241,11 +5136,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4263,11 +5158,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4285,11 +5180,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4307,11 +5202,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4329,11 +5224,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4351,11 +5246,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4373,11 +5268,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4395,11 +5290,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4417,11 +5312,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4439,11 +5334,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4461,11 +5356,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4483,11 +5378,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4505,11 +5400,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4527,11 +5422,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4549,11 +5444,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4571,11 +5466,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4593,11 +5488,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4615,11 +5510,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4637,11 +5532,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4659,11 +5554,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4681,11 +5576,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4703,11 +5598,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -4725,11 +5620,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -4747,11 +5642,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -4769,11 +5664,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -4791,11 +5686,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -4813,11 +5708,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -4835,11 +5730,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -4857,11 +5752,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -4879,11 +5774,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -4901,11 +5796,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -4923,11 +5818,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -4945,11 +5840,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -4967,11 +5862,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -4989,11 +5884,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5011,11 +5906,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5033,11 +5928,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5055,11 +5950,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5077,11 +5972,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5099,11 +5994,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5121,11 +6016,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5143,11 +6038,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5165,11 +6060,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5187,11 +6082,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5209,11 +6104,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5231,11 +6126,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5253,11 +6148,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5275,11 +6170,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5297,11 +6192,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5319,11 +6214,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5341,11 +6236,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5363,11 +6258,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5385,11 +6280,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5407,11 +6302,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5429,11 +6324,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5451,11 +6346,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5473,11 +6368,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="10">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="11">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5495,11 +6390,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5517,11 +6412,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5539,11 +6434,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5561,11 +6456,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5583,11 +6478,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5605,11 +6500,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5627,11 +6522,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5649,11 +6544,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5671,11 +6566,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5693,11 +6588,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -5715,11 +6610,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -5737,11 +6632,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -5759,11 +6654,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -5781,11 +6676,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -5803,11 +6698,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -5825,11 +6720,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -5847,11 +6742,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -5869,11 +6764,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -5891,11 +6786,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -5913,11 +6808,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -5935,11 +6830,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -5957,11 +6852,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -5979,11 +6874,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6001,11 +6896,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6023,11 +6918,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6045,11 +6940,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6067,11 +6962,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6089,11 +6984,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6111,11 +7006,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6133,11 +7028,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6155,11 +7050,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6177,11 +7072,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6199,11 +7094,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6221,11 +7116,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6243,11 +7138,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6265,11 +7160,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6287,11 +7182,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6309,11 +7204,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6331,11 +7226,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6353,11 +7248,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6375,11 +7270,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6397,11 +7292,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6419,11 +7314,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6441,11 +7336,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6463,11 +7358,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6485,11 +7380,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6507,11 +7402,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6529,11 +7424,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6551,11 +7446,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6573,11 +7468,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6595,11 +7490,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6617,11 +7512,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6639,11 +7534,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6661,11 +7556,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6683,11 +7578,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6705,11 +7600,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6727,11 +7622,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6749,11 +7644,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -6771,11 +7666,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -6793,11 +7688,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -6815,11 +7710,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -6837,11 +7732,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -6859,11 +7754,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -6881,11 +7776,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="12">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="13">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -6903,11 +7798,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -6925,11 +7820,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -6947,11 +7842,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -6969,11 +7864,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -6991,11 +7886,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7013,11 +7908,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7035,11 +7930,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7057,11 +7952,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7079,11 +7974,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7101,11 +7996,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7123,11 +8018,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7145,11 +8040,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7167,11 +8062,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7189,11 +8084,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7211,11 +8106,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7233,11 +8128,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7255,11 +8150,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7277,11 +8172,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7299,11 +8194,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7321,11 +8216,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7343,11 +8238,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7365,11 +8260,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7387,11 +8282,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7409,11 +8304,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7431,11 +8326,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7453,11 +8348,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7475,11 +8370,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7497,11 +8392,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7519,11 +8414,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7541,11 +8436,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7563,11 +8458,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7585,11 +8480,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7607,11 +8502,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7629,11 +8524,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7651,11 +8546,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7673,11 +8568,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7695,11 +8590,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -7717,11 +8612,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -7739,11 +8634,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -7761,11 +8656,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -7783,11 +8678,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -7805,11 +8700,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -7827,11 +8722,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -7849,11 +8744,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -7871,11 +8766,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -7893,11 +8788,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -7915,11 +8810,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -7937,11 +8832,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -7959,11 +8854,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -7981,11 +8876,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8003,11 +8898,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8025,11 +8920,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8047,11 +8942,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8069,11 +8964,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8091,11 +8986,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8113,11 +9008,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8135,11 +9030,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8157,11 +9052,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8179,11 +9074,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8201,11 +9096,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8223,11 +9118,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8245,11 +9140,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8267,11 +9162,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8289,11 +9184,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="14">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="15">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8311,11 +9206,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8333,11 +9228,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8355,11 +9250,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8377,11 +9272,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8399,11 +9294,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8421,11 +9316,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8443,11 +9338,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8465,11 +9360,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8487,11 +9382,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8509,11 +9404,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8531,11 +9426,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8553,11 +9448,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8575,11 +9470,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8597,11 +9492,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8619,11 +9514,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8641,11 +9536,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8663,11 +9558,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8685,11 +9580,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8707,11 +9602,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -8729,11 +9624,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -8751,11 +9646,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -8773,11 +9668,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -8795,11 +9690,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -8817,11 +9712,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -8839,11 +9734,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -8861,11 +9756,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -8883,11 +9778,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -8905,11 +9800,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -8927,11 +9822,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -8949,11 +9844,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -8971,11 +9866,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -8993,11 +9888,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9015,11 +9910,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9037,11 +9932,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9059,11 +9954,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9081,11 +9976,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9103,11 +9998,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9125,11 +10020,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9147,11 +10042,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9169,11 +10064,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9191,11 +10086,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9213,11 +10108,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9235,11 +10130,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9257,11 +10152,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9279,11 +10174,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9301,11 +10196,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9323,11 +10218,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9345,11 +10240,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9367,11 +10262,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9389,11 +10284,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9411,11 +10306,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9433,11 +10328,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9455,11 +10350,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9477,11 +10372,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9499,11 +10394,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9521,11 +10416,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9543,11 +10438,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9565,11 +10460,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9587,11 +10482,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9609,11 +10504,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9631,11 +10526,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9653,11 +10548,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9675,11 +10570,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9697,11 +10592,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="16">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="17">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9719,11 +10614,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -9741,11 +10636,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -9763,11 +10658,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -9785,11 +10680,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -9807,11 +10702,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -9829,11 +10724,11 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
@@ -9851,11 +10746,11 @@
       <c r="G397" s="14"/>
       <c r="H397" s="14"/>
       <c r="I397" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J397" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K397" s="16"/>
@@ -9873,11 +10768,11 @@
       <c r="G398" s="14"/>
       <c r="H398" s="14"/>
       <c r="I398" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J398" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K398" s="16"/>
@@ -9895,11 +10790,11 @@
       <c r="G399" s="14"/>
       <c r="H399" s="14"/>
       <c r="I399" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J399" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K399" s="16"/>
@@ -9917,11 +10812,11 @@
       <c r="G400" s="14"/>
       <c r="H400" s="14"/>
       <c r="I400" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J400" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K400" s="16"/>
@@ -9939,11 +10834,11 @@
       <c r="G401" s="14"/>
       <c r="H401" s="14"/>
       <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K401" s="16"/>

--- a/12607125.xlsx
+++ b/12607125.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anuka\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5067808-913F-4429-A577-4F0170FC6308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D98326B7-092C-4144-A96D-B9D255872916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -286,9 +286,6 @@
     <t>Returned home and settled back into my routine.</t>
   </si>
   <si>
-    <t>2026-09-</t>
-  </si>
-  <si>
     <t>Attended classes and studied, had a normal day and felt neutral overall.</t>
   </si>
   <si>
@@ -335,6 +332,15 @@
   </si>
   <si>
     <t>Spent a quiet day with some study and activities, but felt neutral and unsatisfied.</t>
+  </si>
+  <si>
+    <t>Attended classes and worked on coding and study, felt good and satisfied.</t>
+  </si>
+  <si>
+    <t>Went to Chandigarh and spent the day there, felt good and satisfied.</t>
+  </si>
+  <si>
+    <t>Attended classes and studied, felt neutral overall.</t>
   </si>
 </sst>
 </file>
@@ -2169,7 +2175,7 @@
         <v>51</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2261,7 +2267,7 @@
         <v>51</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2307,7 +2313,7 @@
         <v>61</v>
       </c>
       <c r="N31" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2353,7 +2359,7 @@
         <v>61</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2399,7 +2405,7 @@
         <v>51</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2445,7 +2451,7 @@
         <v>51</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2491,7 +2497,7 @@
         <v>51</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2583,7 +2589,7 @@
         <v>61</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2629,7 +2635,7 @@
         <v>51</v>
       </c>
       <c r="N38" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2675,7 +2681,7 @@
         <v>61</v>
       </c>
       <c r="N39" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2721,7 +2727,7 @@
         <v>61</v>
       </c>
       <c r="N40" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2767,7 +2773,7 @@
         <v>61</v>
       </c>
       <c r="N41" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2813,7 +2819,7 @@
         <v>51</v>
       </c>
       <c r="N42" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2859,7 +2865,7 @@
         <v>62</v>
       </c>
       <c r="N43" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2905,7 +2911,7 @@
         <v>51</v>
       </c>
       <c r="N44" s="17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="45" spans="1:14" ht="42.75" x14ac:dyDescent="0.25">
@@ -2951,7 +2957,7 @@
         <v>51</v>
       </c>
       <c r="N45" s="17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2997,7 +3003,7 @@
         <v>61</v>
       </c>
       <c r="N46" s="17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3043,177 +3049,335 @@
         <v>51</v>
       </c>
       <c r="N47" s="17" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="13">
         <v>46286</v>
       </c>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="B48" s="14">
+        <v>389</v>
+      </c>
+      <c r="C48" s="14">
+        <v>23</v>
+      </c>
+      <c r="D48" s="14">
+        <v>56</v>
+      </c>
+      <c r="E48" s="14">
+        <v>101</v>
+      </c>
+      <c r="F48" s="14">
+        <v>250</v>
+      </c>
+      <c r="G48" s="14">
+        <v>5</v>
+      </c>
+      <c r="H48" s="14">
+        <v>110</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>929</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+        <v>511</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B49" s="14">
+        <v>398</v>
+      </c>
+      <c r="C49" s="14">
+        <v>24</v>
+      </c>
+      <c r="D49" s="14">
+        <v>61</v>
+      </c>
+      <c r="E49" s="14">
+        <v>21</v>
+      </c>
+      <c r="F49" s="14">
+        <v>350</v>
+      </c>
+      <c r="G49" s="14">
+        <v>7</v>
+      </c>
+      <c r="H49" s="14">
+        <v>89</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>943</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+        <v>497</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B50" s="14">
+        <v>289</v>
+      </c>
+      <c r="C50" s="14">
+        <v>0</v>
+      </c>
+      <c r="D50" s="14">
+        <v>0</v>
+      </c>
+      <c r="E50" s="14">
+        <v>0</v>
+      </c>
+      <c r="F50" s="14">
+        <v>0</v>
+      </c>
+      <c r="G50" s="14">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14">
+        <v>689</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>978</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+        <v>462</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B51" s="14">
+        <v>402</v>
+      </c>
+      <c r="C51" s="14">
+        <v>23</v>
+      </c>
+      <c r="D51" s="14">
+        <v>67</v>
+      </c>
+      <c r="E51" s="14">
+        <v>21</v>
+      </c>
+      <c r="F51" s="14">
+        <v>150</v>
+      </c>
+      <c r="G51" s="14">
+        <v>3</v>
+      </c>
+      <c r="H51" s="14">
+        <v>112</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>775</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A52" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+        <v>665</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B52" s="14">
+        <v>399</v>
+      </c>
+      <c r="C52" s="14">
+        <v>22</v>
+      </c>
+      <c r="D52" s="14">
+        <v>55</v>
+      </c>
+      <c r="E52" s="14">
+        <v>0</v>
+      </c>
+      <c r="F52" s="14">
+        <v>250</v>
+      </c>
+      <c r="G52" s="14">
+        <v>5</v>
+      </c>
+      <c r="H52" s="14">
+        <v>134</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A53" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+        <v>580</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B53" s="14">
+        <v>402</v>
+      </c>
+      <c r="C53" s="14">
+        <v>23</v>
+      </c>
+      <c r="D53" s="14">
+        <v>72</v>
+      </c>
+      <c r="E53" s="14">
+        <v>12</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>143</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>652</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+        <v>788</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B54" s="14">
+        <v>410</v>
+      </c>
+      <c r="C54" s="14">
+        <v>24</v>
+      </c>
+      <c r="D54" s="14">
+        <v>77</v>
+      </c>
+      <c r="E54" s="14">
+        <v>33</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>132</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>676</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A55" s="13"/>
+        <v>764</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="13">
+        <v>46293</v>
+      </c>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
       <c r="D55" s="14"/>
@@ -3234,8 +3398,10 @@
       <c r="M55" s="16"/>
       <c r="N55" s="17"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A56" s="13"/>
+    <row r="56" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="13">
+        <v>46294</v>
+      </c>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
       <c r="D56" s="14"/>
@@ -3256,8 +3422,10 @@
       <c r="M56" s="16"/>
       <c r="N56" s="17"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A57" s="13"/>
+    <row r="57" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="13">
+        <v>46295</v>
+      </c>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
       <c r="D57" s="14"/>

--- a/12607125.xlsx
+++ b/12607125.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anuka\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D98326B7-092C-4144-A96D-B9D255872916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED07FED0-2734-4768-B190-86C8D8379B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="122">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -341,6 +341,66 @@
   </si>
   <si>
     <t>Attended classes and studied, felt neutral overall.</t>
+  </si>
+  <si>
+    <t>2026-10-</t>
+  </si>
+  <si>
+    <t>There was protest at our university today</t>
+  </si>
+  <si>
+    <t>The protest escalated very much so our university is suspended for 10 days</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>tayed at a friend’s house as the protests escalated significantly.</t>
+  </si>
+  <si>
+    <t>Explored nearby areas with friends, tried different foods, and played games on TV.</t>
+  </si>
+  <si>
+    <t>Spent time with friends exploring nearby places, enjoying food, and playing games.</t>
+  </si>
+  <si>
+    <t>Continued enjoying time with friends, exploring local areas and trying different foods.</t>
+  </si>
+  <si>
+    <t>Went to a vet to check  my friends dog</t>
+  </si>
+  <si>
+    <t>Explored nearby areas and enjoyed spending time with friends.</t>
+  </si>
+  <si>
+    <t>Attended the mandatory online classes and completed the required academic work.</t>
+  </si>
+  <si>
+    <t>Attended mandatory online classes and stayed focused on academics.</t>
+  </si>
+  <si>
+    <t>Attended the mandatory online classes and continued studying.</t>
+  </si>
+  <si>
+    <t>Attended todays doubt clearing session to clear some doubts</t>
+  </si>
+  <si>
+    <t>Completed my minor project and finalized the work.</t>
+  </si>
+  <si>
+    <t>Submitted my minor project and returned to my room near the college.</t>
+  </si>
+  <si>
+    <t>Studied and prepared for the upcoming exams.</t>
+  </si>
+  <si>
+    <t>Appeared for my Computer Networks midterm exam.</t>
+  </si>
+  <si>
+    <t>Appeared for my C++ midterm exam</t>
+  </si>
+  <si>
+    <t>Appeared for my DBMS midterm exam</t>
   </si>
 </sst>
 </file>
@@ -995,7 +1055,7 @@
   <dimension ref="A1:N401"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
@@ -3325,7 +3385,7 @@
         <v>51</v>
       </c>
       <c r="N53" s="17" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3371,391 +3431,795 @@
         <v>61</v>
       </c>
       <c r="N54" s="17" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="13">
         <v>46293</v>
       </c>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+      <c r="B55" s="14">
+        <v>408</v>
+      </c>
+      <c r="C55" s="14">
+        <v>23</v>
+      </c>
+      <c r="D55" s="14">
+        <v>80</v>
+      </c>
+      <c r="E55" s="14">
+        <v>20</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>340</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>871</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+        <v>569</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="56" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="13">
         <v>46294</v>
       </c>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="B56" s="14">
+        <v>410</v>
+      </c>
+      <c r="C56" s="14">
+        <v>0</v>
+      </c>
+      <c r="D56" s="14">
+        <v>0</v>
+      </c>
+      <c r="E56" s="14">
+        <v>0</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>460</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
+        <v>570</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="57" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="13">
         <v>46295</v>
       </c>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="B57" s="14">
+        <v>422</v>
+      </c>
+      <c r="C57" s="14">
+        <v>0</v>
+      </c>
+      <c r="D57" s="14">
+        <v>0</v>
+      </c>
+      <c r="E57" s="14">
+        <v>0</v>
+      </c>
+      <c r="F57" s="14">
+        <v>0</v>
+      </c>
+      <c r="G57" s="14">
+        <v>0</v>
+      </c>
+      <c r="H57" s="14">
+        <v>422</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>844</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+        <v>596</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B58" s="14">
+        <v>428</v>
+      </c>
+      <c r="C58" s="14">
+        <v>12</v>
+      </c>
+      <c r="D58" s="14">
+        <v>0</v>
+      </c>
+      <c r="E58" s="14">
+        <v>0</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>389</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>829</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+        <v>611</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B59" s="14">
+        <v>458</v>
+      </c>
+      <c r="C59" s="14">
+        <v>14</v>
+      </c>
+      <c r="D59" s="14">
+        <v>0</v>
+      </c>
+      <c r="E59" s="14">
+        <v>0</v>
+      </c>
+      <c r="F59" s="14">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <v>388</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+        <v>580</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B60" s="14">
+        <v>468</v>
+      </c>
+      <c r="C60" s="14">
+        <v>13</v>
+      </c>
+      <c r="D60" s="14">
+        <v>0</v>
+      </c>
+      <c r="E60" s="14">
+        <v>0</v>
+      </c>
+      <c r="F60" s="14">
+        <v>0</v>
+      </c>
+      <c r="G60" s="14">
+        <v>0</v>
+      </c>
+      <c r="H60" s="14">
+        <v>391</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>872</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+        <v>568</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B61" s="14">
+        <v>489</v>
+      </c>
+      <c r="C61" s="14">
+        <v>12</v>
+      </c>
+      <c r="D61" s="14">
+        <v>0</v>
+      </c>
+      <c r="E61" s="14">
+        <v>0</v>
+      </c>
+      <c r="F61" s="14">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14">
+        <v>0</v>
+      </c>
+      <c r="H61" s="14">
+        <v>385</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>886</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+        <v>554</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B62" s="14">
+        <v>388</v>
+      </c>
+      <c r="C62" s="14">
+        <v>14</v>
+      </c>
+      <c r="D62" s="14">
+        <v>33</v>
+      </c>
+      <c r="E62" s="14">
+        <v>21</v>
+      </c>
+      <c r="F62" s="14">
+        <v>250</v>
+      </c>
+      <c r="G62" s="14">
+        <v>4</v>
+      </c>
+      <c r="H62" s="14">
+        <v>181</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>887</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="17"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+        <v>553</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N62" s="17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B63" s="14">
+        <v>381</v>
+      </c>
+      <c r="C63" s="14">
+        <v>11</v>
+      </c>
+      <c r="D63" s="14">
+        <v>32</v>
+      </c>
+      <c r="E63" s="14">
+        <v>21</v>
+      </c>
+      <c r="F63" s="14">
+        <v>350</v>
+      </c>
+      <c r="G63" s="14">
+        <v>7</v>
+      </c>
+      <c r="H63" s="14">
+        <v>134</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>929</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="17"/>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+        <v>511</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N63" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B64" s="14">
+        <v>382</v>
+      </c>
+      <c r="C64" s="14">
+        <v>12</v>
+      </c>
+      <c r="D64" s="14">
+        <v>36</v>
+      </c>
+      <c r="E64" s="14">
+        <v>23</v>
+      </c>
+      <c r="F64" s="14">
+        <v>300</v>
+      </c>
+      <c r="G64" s="14">
+        <v>6</v>
+      </c>
+      <c r="H64" s="14">
+        <v>143</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>896</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="17"/>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+        <v>544</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N64" s="17" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B65" s="14">
+        <v>381</v>
+      </c>
+      <c r="C65" s="14">
+        <v>14</v>
+      </c>
+      <c r="D65" s="14">
+        <v>40</v>
+      </c>
+      <c r="E65" s="14">
+        <v>20</v>
+      </c>
+      <c r="F65" s="14">
+        <v>200</v>
+      </c>
+      <c r="G65" s="14">
+        <v>2</v>
+      </c>
+      <c r="H65" s="14">
+        <v>231</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>886</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="17"/>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
+        <v>554</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N65" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B66" s="14">
+        <v>392</v>
+      </c>
+      <c r="C66" s="14">
+        <v>18</v>
+      </c>
+      <c r="D66" s="14">
+        <v>35</v>
+      </c>
+      <c r="E66" s="14">
+        <v>25</v>
+      </c>
+      <c r="F66" s="14">
+        <v>0</v>
+      </c>
+      <c r="G66" s="14">
+        <v>0</v>
+      </c>
+      <c r="H66" s="14">
+        <v>341</v>
+      </c>
+      <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
+        <v>811</v>
+      </c>
+      <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="17"/>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="15" t="str">
+        <v>629</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N66" s="17" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B67" s="14">
+        <v>212</v>
+      </c>
+      <c r="C67" s="14">
+        <v>0</v>
+      </c>
+      <c r="D67" s="14">
+        <v>70</v>
+      </c>
+      <c r="E67" s="14">
+        <v>0</v>
+      </c>
+      <c r="F67" s="14">
+        <v>0</v>
+      </c>
+      <c r="G67" s="14">
+        <v>0</v>
+      </c>
+      <c r="H67" s="14">
+        <v>450</v>
+      </c>
+      <c r="I67" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
+        <v>732</v>
+      </c>
+      <c r="J67" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
-      <c r="N67" s="17"/>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A68" s="13"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="15" t="str">
+        <v>708</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N67" s="17" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B68" s="14">
+        <v>388</v>
+      </c>
+      <c r="C68" s="14">
+        <v>23</v>
+      </c>
+      <c r="D68" s="14">
+        <v>140</v>
+      </c>
+      <c r="E68" s="14">
+        <v>0</v>
+      </c>
+      <c r="F68" s="14">
+        <v>0</v>
+      </c>
+      <c r="G68" s="14">
+        <v>0</v>
+      </c>
+      <c r="H68" s="14">
+        <v>118</v>
+      </c>
+      <c r="I68" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="15" t="str">
+        <v>669</v>
+      </c>
+      <c r="J68" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
-      <c r="N68" s="17"/>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A69" s="13"/>
-      <c r="B69" s="14"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="15" t="str">
+        <v>771</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N68" s="17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="13">
+        <v>46307</v>
+      </c>
+      <c r="B69" s="14">
+        <v>325</v>
+      </c>
+      <c r="C69" s="14">
+        <v>20</v>
+      </c>
+      <c r="D69" s="14">
+        <v>240</v>
+      </c>
+      <c r="E69" s="14">
+        <v>0</v>
+      </c>
+      <c r="F69" s="14">
+        <v>0</v>
+      </c>
+      <c r="G69" s="14">
+        <v>0</v>
+      </c>
+      <c r="H69" s="14">
+        <v>140</v>
+      </c>
+      <c r="I69" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="15" t="str">
+        <v>725</v>
+      </c>
+      <c r="J69" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
-      <c r="N69" s="17"/>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A70" s="13"/>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="15" t="str">
+        <v>715</v>
+      </c>
+      <c r="K69" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L69" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M69" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N69" s="17" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B70" s="14">
+        <v>324</v>
+      </c>
+      <c r="C70" s="14">
+        <v>21</v>
+      </c>
+      <c r="D70" s="14">
+        <v>254</v>
+      </c>
+      <c r="E70" s="14">
+        <v>55</v>
+      </c>
+      <c r="F70" s="14">
+        <v>0</v>
+      </c>
+      <c r="G70" s="14">
+        <v>0</v>
+      </c>
+      <c r="H70" s="14">
+        <v>180</v>
+      </c>
+      <c r="I70" s="15">
         <f t="shared" ref="I70:I133" si="6">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="15" t="str">
+        <v>834</v>
+      </c>
+      <c r="J70" s="15">
         <f t="shared" ref="J70:J133" si="7">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
-      <c r="N70" s="17"/>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A71" s="13"/>
-      <c r="B71" s="14"/>
-      <c r="C71" s="14"/>
-      <c r="D71" s="14"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="15" t="str">
+        <v>606</v>
+      </c>
+      <c r="K70" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L70" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M70" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N70" s="17" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B71" s="14">
+        <v>320</v>
+      </c>
+      <c r="C71" s="14">
+        <v>22</v>
+      </c>
+      <c r="D71" s="14">
+        <v>244</v>
+      </c>
+      <c r="E71" s="14">
+        <v>0</v>
+      </c>
+      <c r="F71" s="14">
+        <v>0</v>
+      </c>
+      <c r="G71" s="14">
+        <v>0</v>
+      </c>
+      <c r="H71" s="14">
+        <v>175</v>
+      </c>
+      <c r="I71" s="15">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J71" s="15" t="str">
+        <v>761</v>
+      </c>
+      <c r="J71" s="15">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K71" s="16"/>
-      <c r="L71" s="16"/>
-      <c r="M71" s="16"/>
-      <c r="N71" s="17"/>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A72" s="13"/>
+        <v>679</v>
+      </c>
+      <c r="K71" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L71" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M71" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N71" s="17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="13">
+        <v>46310</v>
+      </c>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
       <c r="D72" s="14"/>
@@ -3777,7 +4241,9 @@
       <c r="N72" s="17"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A73" s="13"/>
+      <c r="A73" s="13" t="s">
+        <v>102</v>
+      </c>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
       <c r="D73" s="14"/>
@@ -3799,7 +4265,9 @@
       <c r="N73" s="17"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A74" s="13"/>
+      <c r="A74" s="13" t="s">
+        <v>102</v>
+      </c>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
       <c r="D74" s="14"/>
@@ -3821,7 +4289,9 @@
       <c r="N74" s="17"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A75" s="13"/>
+      <c r="A75" s="13" t="s">
+        <v>102</v>
+      </c>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
       <c r="D75" s="14"/>
@@ -3843,7 +4313,9 @@
       <c r="N75" s="17"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A76" s="13"/>
+      <c r="A76" s="13" t="s">
+        <v>102</v>
+      </c>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
       <c r="D76" s="14"/>
@@ -3865,7 +4337,9 @@
       <c r="N76" s="17"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A77" s="13"/>
+      <c r="A77" s="13" t="s">
+        <v>102</v>
+      </c>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
       <c r="D77" s="14"/>
@@ -3887,7 +4361,9 @@
       <c r="N77" s="17"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A78" s="13"/>
+      <c r="A78" s="13" t="s">
+        <v>102</v>
+      </c>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
       <c r="D78" s="14"/>

--- a/12607125.xlsx
+++ b/12607125.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anuka\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED07FED0-2734-4768-B190-86C8D8379B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F0340D-ED3D-4F4F-AE7C-6B1B8F311404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="128">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -401,6 +401,24 @@
   </si>
   <si>
     <t>Appeared for my DBMS midterm exam</t>
+  </si>
+  <si>
+    <t>Prepared for my analytical exam</t>
+  </si>
+  <si>
+    <t>Analytical exam went better than expected</t>
+  </si>
+  <si>
+    <t>English communication exam went well today</t>
+  </si>
+  <si>
+    <t>Took a break for the whole day</t>
+  </si>
+  <si>
+    <t>Continued with my regular classes</t>
+  </si>
+  <si>
+    <t>Had a day off for Maha Navami</t>
   </si>
 </sst>
 </file>
@@ -4220,172 +4238,328 @@
       <c r="A72" s="13">
         <v>46310</v>
       </c>
-      <c r="B72" s="14"/>
-      <c r="C72" s="14"/>
-      <c r="D72" s="14"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="15" t="str">
+      <c r="B72" s="14">
+        <v>422</v>
+      </c>
+      <c r="C72" s="14">
+        <v>23</v>
+      </c>
+      <c r="D72" s="14">
+        <v>330</v>
+      </c>
+      <c r="E72" s="14">
+        <v>0</v>
+      </c>
+      <c r="F72" s="14">
+        <v>0</v>
+      </c>
+      <c r="G72" s="14">
+        <v>0</v>
+      </c>
+      <c r="H72" s="14">
+        <v>125</v>
+      </c>
+      <c r="I72" s="15">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J72" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J72" s="15">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
-      <c r="N72" s="17"/>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A73" s="13" t="s">
+        <v>540</v>
+      </c>
+      <c r="K72" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L72" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M72" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N72" s="17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B73" s="14">
+        <v>322</v>
+      </c>
+      <c r="C73" s="14">
+        <v>25</v>
+      </c>
+      <c r="D73" s="14">
+        <v>245</v>
+      </c>
+      <c r="E73" s="14">
+        <v>0</v>
+      </c>
+      <c r="F73" s="14">
+        <v>0</v>
+      </c>
+      <c r="G73" s="14">
+        <v>0</v>
+      </c>
+      <c r="H73" s="14">
+        <v>128</v>
+      </c>
+      <c r="I73" s="15">
+        <f t="shared" si="6"/>
+        <v>720</v>
+      </c>
+      <c r="J73" s="15">
+        <f t="shared" si="7"/>
+        <v>720</v>
+      </c>
+      <c r="K73" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L73" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M73" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N73" s="17" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B74" s="14">
+        <v>320</v>
+      </c>
+      <c r="C74" s="14">
+        <v>30</v>
+      </c>
+      <c r="D74" s="14">
+        <v>108</v>
+      </c>
+      <c r="E74" s="14">
+        <v>0</v>
+      </c>
+      <c r="F74" s="14">
+        <v>0</v>
+      </c>
+      <c r="G74" s="14">
+        <v>0</v>
+      </c>
+      <c r="H74" s="14">
+        <v>120</v>
+      </c>
+      <c r="I74" s="15">
+        <f t="shared" si="6"/>
+        <v>578</v>
+      </c>
+      <c r="J74" s="15">
+        <f t="shared" si="7"/>
+        <v>862</v>
+      </c>
+      <c r="K74" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L74" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M74" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N74" s="17" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B75" s="14">
+        <v>428</v>
+      </c>
+      <c r="C75" s="14">
+        <v>30</v>
+      </c>
+      <c r="D75" s="14">
+        <v>0</v>
+      </c>
+      <c r="E75" s="14">
+        <v>0</v>
+      </c>
+      <c r="F75" s="14">
+        <v>0</v>
+      </c>
+      <c r="G75" s="14">
+        <v>0</v>
+      </c>
+      <c r="H75" s="14">
+        <v>284</v>
+      </c>
+      <c r="I75" s="15">
+        <f t="shared" si="6"/>
+        <v>742</v>
+      </c>
+      <c r="J75" s="15">
+        <f t="shared" si="7"/>
+        <v>698</v>
+      </c>
+      <c r="K75" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L75" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M75" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N75" s="17" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="13">
+        <v>46314</v>
+      </c>
+      <c r="B76" s="14">
+        <v>402</v>
+      </c>
+      <c r="C76" s="14">
+        <v>32</v>
+      </c>
+      <c r="D76" s="14">
+        <v>62</v>
+      </c>
+      <c r="E76" s="14">
+        <v>20</v>
+      </c>
+      <c r="F76" s="14">
+        <v>250</v>
+      </c>
+      <c r="G76" s="14">
+        <v>5</v>
+      </c>
+      <c r="H76" s="14">
+        <v>120</v>
+      </c>
+      <c r="I76" s="15">
+        <f t="shared" si="6"/>
+        <v>886</v>
+      </c>
+      <c r="J76" s="15">
+        <f t="shared" si="7"/>
+        <v>554</v>
+      </c>
+      <c r="K76" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L76" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M76" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N76" s="17" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B77" s="14">
+        <v>420</v>
+      </c>
+      <c r="C77" s="14">
+        <v>32</v>
+      </c>
+      <c r="D77" s="14">
+        <v>56</v>
+      </c>
+      <c r="E77" s="14">
+        <v>43</v>
+      </c>
+      <c r="F77" s="14">
+        <v>0</v>
+      </c>
+      <c r="G77" s="14">
+        <v>0</v>
+      </c>
+      <c r="H77" s="14">
+        <v>184</v>
+      </c>
+      <c r="I77" s="15">
+        <f t="shared" si="6"/>
+        <v>735</v>
+      </c>
+      <c r="J77" s="15">
+        <f t="shared" si="7"/>
+        <v>705</v>
+      </c>
+      <c r="K77" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L77" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M77" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N77" s="17" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B78" s="14">
+        <v>402</v>
+      </c>
+      <c r="C78" s="14">
+        <v>28</v>
+      </c>
+      <c r="D78" s="14">
+        <v>62</v>
+      </c>
+      <c r="E78" s="14">
+        <v>22</v>
+      </c>
+      <c r="F78" s="14">
+        <v>300</v>
+      </c>
+      <c r="G78" s="14">
+        <v>6</v>
+      </c>
+      <c r="H78" s="14">
+        <v>120</v>
+      </c>
+      <c r="I78" s="15">
+        <f t="shared" si="6"/>
+        <v>934</v>
+      </c>
+      <c r="J78" s="15">
+        <f t="shared" si="7"/>
+        <v>506</v>
+      </c>
+      <c r="K78" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L78" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M78" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N78" s="17" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A79" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="B73" s="14"/>
-      <c r="C73" s="14"/>
-      <c r="D73" s="14"/>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="15" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J73" s="15" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
-      <c r="N73" s="17"/>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A74" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="B74" s="14"/>
-      <c r="C74" s="14"/>
-      <c r="D74" s="14"/>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="15" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J74" s="15" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="16"/>
-      <c r="N74" s="17"/>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A75" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="B75" s="14"/>
-      <c r="C75" s="14"/>
-      <c r="D75" s="14"/>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
-      <c r="I75" s="15" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J75" s="15" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K75" s="16"/>
-      <c r="L75" s="16"/>
-      <c r="M75" s="16"/>
-      <c r="N75" s="17"/>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A76" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="B76" s="14"/>
-      <c r="C76" s="14"/>
-      <c r="D76" s="14"/>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
-      <c r="I76" s="15" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J76" s="15" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K76" s="16"/>
-      <c r="L76" s="16"/>
-      <c r="M76" s="16"/>
-      <c r="N76" s="17"/>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A77" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="B77" s="14"/>
-      <c r="C77" s="14"/>
-      <c r="D77" s="14"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
-      <c r="G77" s="14"/>
-      <c r="H77" s="14"/>
-      <c r="I77" s="15" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J77" s="15" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K77" s="16"/>
-      <c r="L77" s="16"/>
-      <c r="M77" s="16"/>
-      <c r="N77" s="17"/>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A78" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="B78" s="14"/>
-      <c r="C78" s="14"/>
-      <c r="D78" s="14"/>
-      <c r="E78" s="14"/>
-      <c r="F78" s="14"/>
-      <c r="G78" s="14"/>
-      <c r="H78" s="14"/>
-      <c r="I78" s="15" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J78" s="15" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K78" s="16"/>
-      <c r="L78" s="16"/>
-      <c r="M78" s="16"/>
-      <c r="N78" s="17"/>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A79" s="13"/>
       <c r="B79" s="14"/>
       <c r="C79" s="14"/>
       <c r="D79" s="14"/>
@@ -4407,7 +4581,9 @@
       <c r="N79" s="17"/>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A80" s="13"/>
+      <c r="A80" s="13" t="s">
+        <v>102</v>
+      </c>
       <c r="B80" s="14"/>
       <c r="C80" s="14"/>
       <c r="D80" s="14"/>
@@ -4429,7 +4605,9 @@
       <c r="N80" s="17"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A81" s="13"/>
+      <c r="A81" s="13" t="s">
+        <v>102</v>
+      </c>
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
       <c r="D81" s="14"/>
@@ -4451,7 +4629,9 @@
       <c r="N81" s="17"/>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A82" s="13"/>
+      <c r="A82" s="13" t="s">
+        <v>102</v>
+      </c>
       <c r="B82" s="14"/>
       <c r="C82" s="14"/>
       <c r="D82" s="14"/>
@@ -4473,7 +4653,9 @@
       <c r="N82" s="17"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A83" s="13"/>
+      <c r="A83" s="13" t="s">
+        <v>102</v>
+      </c>
       <c r="B83" s="14"/>
       <c r="C83" s="14"/>
       <c r="D83" s="14"/>
@@ -4495,7 +4677,9 @@
       <c r="N83" s="17"/>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A84" s="13"/>
+      <c r="A84" s="13" t="s">
+        <v>102</v>
+      </c>
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
       <c r="D84" s="14"/>
@@ -4517,7 +4701,9 @@
       <c r="N84" s="17"/>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A85" s="13"/>
+      <c r="A85" s="13" t="s">
+        <v>102</v>
+      </c>
       <c r="B85" s="14"/>
       <c r="C85" s="14"/>
       <c r="D85" s="14"/>
@@ -4539,7 +4725,9 @@
       <c r="N85" s="17"/>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A86" s="13"/>
+      <c r="A86" s="13" t="s">
+        <v>102</v>
+      </c>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
       <c r="D86" s="14"/>
@@ -4561,7 +4749,9 @@
       <c r="N86" s="17"/>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A87" s="13"/>
+      <c r="A87" s="13" t="s">
+        <v>102</v>
+      </c>
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
       <c r="D87" s="14"/>
@@ -4583,7 +4773,9 @@
       <c r="N87" s="17"/>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A88" s="13"/>
+      <c r="A88" s="13" t="s">
+        <v>102</v>
+      </c>
       <c r="B88" s="14"/>
       <c r="C88" s="14"/>
       <c r="D88" s="14"/>

--- a/12607125.xlsx
+++ b/12607125.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anuka\Downloads\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F0340D-ED3D-4F4F-AE7C-6B1B8F311404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A52257A-F4AA-413E-974C-B6682125290B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="133">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -343,9 +343,6 @@
     <t>Attended classes and studied, felt neutral overall.</t>
   </si>
   <si>
-    <t>2026-10-</t>
-  </si>
-  <si>
     <t>There was protest at our university today</t>
   </si>
   <si>
@@ -419,6 +416,24 @@
   </si>
   <si>
     <t>Had a day off for Maha Navami</t>
+  </si>
+  <si>
+    <t>Attended my regular classes</t>
+  </si>
+  <si>
+    <t>Had our DBMS viva today for CA2</t>
+  </si>
+  <si>
+    <t>Spent time studyng my CPP project topic</t>
+  </si>
+  <si>
+    <t>Worked on my cpp project today</t>
+  </si>
+  <si>
+    <t>Completed my cpp project as today was my last date for submission</t>
+  </si>
+  <si>
+    <t>Had a normal day attending my regular claases</t>
   </si>
 </sst>
 </file>
@@ -3403,7 +3418,7 @@
         <v>51</v>
       </c>
       <c r="N53" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3449,7 +3464,7 @@
         <v>61</v>
       </c>
       <c r="N54" s="17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3495,7 +3510,7 @@
         <v>51</v>
       </c>
       <c r="N55" s="17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="56" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3541,7 +3556,7 @@
         <v>61</v>
       </c>
       <c r="N56" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="57" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.25">
@@ -3587,7 +3602,7 @@
         <v>61</v>
       </c>
       <c r="N57" s="17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3633,7 +3648,7 @@
         <v>61</v>
       </c>
       <c r="N58" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="59" spans="1:14" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3679,7 +3694,7 @@
         <v>61</v>
       </c>
       <c r="N59" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="60" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3725,7 +3740,7 @@
         <v>61</v>
       </c>
       <c r="N60" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="61" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.25">
@@ -3771,7 +3786,7 @@
         <v>61</v>
       </c>
       <c r="N61" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="62" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3811,13 +3826,13 @@
         <v>49</v>
       </c>
       <c r="L62" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M62" s="16" t="s">
         <v>61</v>
       </c>
       <c r="N62" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3863,7 +3878,7 @@
         <v>61</v>
       </c>
       <c r="N63" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="64" spans="1:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3909,7 +3924,7 @@
         <v>61</v>
       </c>
       <c r="N64" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="65" spans="1:14" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3955,7 +3970,7 @@
         <v>51</v>
       </c>
       <c r="N65" s="17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="66" spans="1:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4001,7 +4016,7 @@
         <v>51</v>
       </c>
       <c r="N66" s="17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="67" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -4047,7 +4062,7 @@
         <v>62</v>
       </c>
       <c r="N67" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:14" ht="54" customHeight="1" x14ac:dyDescent="0.25">
@@ -4093,7 +4108,7 @@
         <v>51</v>
       </c>
       <c r="N68" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="69" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4139,7 +4154,7 @@
         <v>51</v>
       </c>
       <c r="N69" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="70" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4185,7 +4200,7 @@
         <v>51</v>
       </c>
       <c r="N70" s="17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="71" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4231,7 +4246,7 @@
         <v>51</v>
       </c>
       <c r="N71" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="72" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4277,7 +4292,7 @@
         <v>51</v>
       </c>
       <c r="N72" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="73" spans="1:14" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4323,7 +4338,7 @@
         <v>51</v>
       </c>
       <c r="N73" s="17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="74" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4369,7 +4384,7 @@
         <v>61</v>
       </c>
       <c r="N74" s="17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="75" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4415,7 +4430,7 @@
         <v>61</v>
       </c>
       <c r="N75" s="17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4461,7 +4476,7 @@
         <v>51</v>
       </c>
       <c r="N76" s="17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="77" spans="1:14" ht="48" customHeight="1" x14ac:dyDescent="0.25">
@@ -4507,7 +4522,7 @@
         <v>61</v>
       </c>
       <c r="N77" s="17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="78" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -4553,180 +4568,334 @@
         <v>51</v>
       </c>
       <c r="N78" s="17" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A79" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="B79" s="14"/>
-      <c r="C79" s="14"/>
-      <c r="D79" s="14"/>
-      <c r="E79" s="14"/>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
-      <c r="H79" s="14"/>
-      <c r="I79" s="15" t="str">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="13">
+        <v>46317</v>
+      </c>
+      <c r="B79" s="14">
+        <v>405</v>
+      </c>
+      <c r="C79" s="14">
+        <v>25</v>
+      </c>
+      <c r="D79" s="14">
+        <v>60</v>
+      </c>
+      <c r="E79" s="14">
+        <v>15</v>
+      </c>
+      <c r="F79" s="14">
+        <v>200</v>
+      </c>
+      <c r="G79" s="14">
+        <v>4</v>
+      </c>
+      <c r="H79" s="14">
+        <v>110</v>
+      </c>
+      <c r="I79" s="15">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J79" s="15" t="str">
+        <v>815</v>
+      </c>
+      <c r="J79" s="15">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K79" s="16"/>
-      <c r="L79" s="16"/>
-      <c r="M79" s="16"/>
-      <c r="N79" s="17"/>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A80" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="B80" s="14"/>
-      <c r="C80" s="14"/>
-      <c r="D80" s="14"/>
-      <c r="E80" s="14"/>
-      <c r="F80" s="14"/>
-      <c r="G80" s="14"/>
-      <c r="H80" s="14"/>
-      <c r="I80" s="15" t="str">
+        <v>625</v>
+      </c>
+      <c r="K79" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L79" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M79" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N79" s="17" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B80" s="14">
+        <v>410</v>
+      </c>
+      <c r="C80" s="14">
+        <v>30</v>
+      </c>
+      <c r="D80" s="14">
+        <v>90</v>
+      </c>
+      <c r="E80" s="14">
+        <v>25</v>
+      </c>
+      <c r="F80" s="14">
+        <v>250</v>
+      </c>
+      <c r="G80" s="14">
+        <v>5</v>
+      </c>
+      <c r="H80" s="14">
+        <v>108</v>
+      </c>
+      <c r="I80" s="15">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J80" s="15" t="str">
+        <v>913</v>
+      </c>
+      <c r="J80" s="15">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K80" s="16"/>
-      <c r="L80" s="16"/>
-      <c r="M80" s="16"/>
-      <c r="N80" s="17"/>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A81" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="B81" s="14"/>
-      <c r="C81" s="14"/>
-      <c r="D81" s="14"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14"/>
-      <c r="H81" s="14"/>
-      <c r="I81" s="15" t="str">
+        <v>527</v>
+      </c>
+      <c r="K80" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L80" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M80" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N80" s="17" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="13">
+        <v>46319</v>
+      </c>
+      <c r="B81" s="14">
+        <v>520</v>
+      </c>
+      <c r="C81" s="14">
+        <v>35</v>
+      </c>
+      <c r="D81" s="14">
+        <v>120</v>
+      </c>
+      <c r="E81" s="14">
+        <v>15</v>
+      </c>
+      <c r="F81" s="14">
+        <v>0</v>
+      </c>
+      <c r="G81" s="14">
+        <v>0</v>
+      </c>
+      <c r="H81" s="14">
+        <v>110</v>
+      </c>
+      <c r="I81" s="15">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J81" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J81" s="15">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K81" s="16"/>
-      <c r="L81" s="16"/>
-      <c r="M81" s="16"/>
-      <c r="N81" s="17"/>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A82" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="B82" s="14"/>
-      <c r="C82" s="14"/>
-      <c r="D82" s="14"/>
-      <c r="E82" s="14"/>
-      <c r="F82" s="14"/>
-      <c r="G82" s="14"/>
-      <c r="H82" s="14"/>
-      <c r="I82" s="15" t="str">
+        <v>640</v>
+      </c>
+      <c r="K81" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L81" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M81" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N81" s="17" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="13">
+        <v>46320</v>
+      </c>
+      <c r="B82" s="14">
+        <v>530</v>
+      </c>
+      <c r="C82" s="14">
+        <v>30</v>
+      </c>
+      <c r="D82" s="14">
+        <v>130</v>
+      </c>
+      <c r="E82" s="14">
+        <v>60</v>
+      </c>
+      <c r="F82" s="14">
+        <v>0</v>
+      </c>
+      <c r="G82" s="14">
+        <v>0</v>
+      </c>
+      <c r="H82" s="14">
+        <v>105</v>
+      </c>
+      <c r="I82" s="15">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J82" s="15" t="str">
+        <v>855</v>
+      </c>
+      <c r="J82" s="15">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K82" s="16"/>
-      <c r="L82" s="16"/>
-      <c r="M82" s="16"/>
-      <c r="N82" s="17"/>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A83" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="B83" s="14"/>
-      <c r="C83" s="14"/>
-      <c r="D83" s="14"/>
-      <c r="E83" s="14"/>
-      <c r="F83" s="14"/>
-      <c r="G83" s="14"/>
-      <c r="H83" s="14"/>
-      <c r="I83" s="15" t="str">
+        <v>585</v>
+      </c>
+      <c r="K82" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L82" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M82" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N82" s="17" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B83" s="14">
+        <v>520</v>
+      </c>
+      <c r="C83" s="14">
+        <v>30</v>
+      </c>
+      <c r="D83" s="14">
+        <v>110</v>
+      </c>
+      <c r="E83" s="14">
+        <v>50</v>
+      </c>
+      <c r="F83" s="14">
+        <v>0</v>
+      </c>
+      <c r="G83" s="14">
+        <v>0</v>
+      </c>
+      <c r="H83" s="14">
+        <v>110</v>
+      </c>
+      <c r="I83" s="15">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J83" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J83" s="15">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K83" s="16"/>
-      <c r="L83" s="16"/>
-      <c r="M83" s="16"/>
-      <c r="N83" s="17"/>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A84" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="B84" s="14"/>
-      <c r="C84" s="14"/>
-      <c r="D84" s="14"/>
-      <c r="E84" s="14"/>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14"/>
-      <c r="H84" s="14"/>
-      <c r="I84" s="15" t="str">
+        <v>620</v>
+      </c>
+      <c r="K83" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L83" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M83" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N83" s="17" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B84" s="14">
+        <v>403</v>
+      </c>
+      <c r="C84" s="14">
+        <v>30</v>
+      </c>
+      <c r="D84" s="14">
+        <v>60</v>
+      </c>
+      <c r="E84" s="14">
+        <v>20</v>
+      </c>
+      <c r="F84" s="14">
+        <v>350</v>
+      </c>
+      <c r="G84" s="14">
+        <v>7</v>
+      </c>
+      <c r="H84" s="14">
+        <v>108</v>
+      </c>
+      <c r="I84" s="15">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J84" s="15" t="str">
+        <v>971</v>
+      </c>
+      <c r="J84" s="15">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K84" s="16"/>
-      <c r="L84" s="16"/>
-      <c r="M84" s="16"/>
-      <c r="N84" s="17"/>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A85" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="B85" s="14"/>
-      <c r="C85" s="14"/>
-      <c r="D85" s="14"/>
-      <c r="E85" s="14"/>
-      <c r="F85" s="14"/>
-      <c r="G85" s="14"/>
-      <c r="H85" s="14"/>
-      <c r="I85" s="15" t="str">
+        <v>469</v>
+      </c>
+      <c r="K84" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L84" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M84" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N84" s="17" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B85" s="14">
+        <v>402</v>
+      </c>
+      <c r="C85" s="14">
+        <v>30</v>
+      </c>
+      <c r="D85" s="14">
+        <v>50</v>
+      </c>
+      <c r="E85" s="14">
+        <v>15</v>
+      </c>
+      <c r="F85" s="14">
+        <v>300</v>
+      </c>
+      <c r="G85" s="14">
+        <v>5</v>
+      </c>
+      <c r="H85" s="14">
+        <v>110</v>
+      </c>
+      <c r="I85" s="15">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="J85" s="15" t="str">
+        <v>907</v>
+      </c>
+      <c r="J85" s="15">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="K85" s="16"/>
-      <c r="L85" s="16"/>
-      <c r="M85" s="16"/>
-      <c r="N85" s="17"/>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A86" s="13" t="s">
-        <v>102</v>
+        <v>533</v>
+      </c>
+      <c r="K85" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L85" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M85" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N85" s="17" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="13">
+        <v>46324</v>
       </c>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
@@ -4748,9 +4917,9 @@
       <c r="M86" s="16"/>
       <c r="N86" s="17"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A87" s="13" t="s">
-        <v>102</v>
+    <row r="87" spans="1:14" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="13">
+        <v>46325</v>
       </c>
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
@@ -4772,9 +4941,9 @@
       <c r="M87" s="16"/>
       <c r="N87" s="17"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A88" s="13" t="s">
-        <v>102</v>
+    <row r="88" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="13">
+        <v>46316</v>
       </c>
       <c r="B88" s="14"/>
       <c r="C88" s="14"/>
